--- a/2_Formulas_Functions/2_Functions_Intro.xlsx
+++ b/2_Formulas_Functions/2_Functions_Intro.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nazil\1 A CHARUSAT\1 Visual Studio Code\Personal\DOA\1_Excel_DOA_Course\Excel_Data_Analytics_Course\2_Formulas_Functions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1 Visual Studio Code\Personal\DOA\1_Excel_DOA_Course\Excel_Data_Analytics_Course\2_Formulas_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3239D18C-E77B-436A-BC8C-E73FB5A5539F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED6870B5-D912-4C15-B585-508CF7EAC1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{8CC555B5-3E06-43B6-9E5B-C0A1D3498DA4}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{8CC555B5-3E06-43B6-9E5B-C0A1D3498DA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="9" r:id="rId1"/>
     <sheet name="Final" sheetId="7" r:id="rId2"/>
     <sheet name="Errors" sheetId="8" r:id="rId3"/>
+    <sheet name="Final (2)" sheetId="10" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -58,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="50">
   <si>
     <t>Data Scientist</t>
   </si>
@@ -205,6 +206,9 @@
   </si>
   <si>
     <t>The formula refers to a cell that isn’t valid (usually deleted cell)</t>
+  </si>
+  <si>
+    <t>Meets Goals Count (Reference)</t>
   </si>
 </sst>
 </file>
@@ -1791,7 +1795,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.44140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="12.21875" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.5546875" style="1" customWidth="1"/>
@@ -2527,10 +2531,10 @@
     </row>
     <row r="17" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="12" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="C17" s="35">
-        <f>COUNTIF($C$3:$C$12, "&lt;=" &amp; S3)</f>
+        <f>COUNTIF($C$3:$C$12, "&lt;=" &amp;S3)</f>
         <v>6</v>
       </c>
       <c r="D17" s="35">
@@ -2653,4 +2657,763 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9B2F582-31DF-4E81-ABE6-6787061D9B07}">
+  <dimension ref="B1:S17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="1" hidden="1" customWidth="1"/>
+    <col min="8" max="9" width="11" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.21875" style="1" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="23.5546875" style="1" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.109375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="11.88671875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9" style="1"/>
+    <col min="18" max="18" width="15.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G1" s="28"/>
+    </row>
+    <row r="2" spans="2:19" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="O2" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="R2" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="S2" s="1"/>
+    </row>
+    <row r="3" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="6">
+        <v>5</v>
+      </c>
+      <c r="D3" s="6">
+        <v>120000</v>
+      </c>
+      <c r="E3" s="7">
+        <v>10000</v>
+      </c>
+      <c r="F3" s="26">
+        <f>C3</f>
+        <v>5</v>
+      </c>
+      <c r="G3" s="22">
+        <f>D3+E3</f>
+        <v>130000</v>
+      </c>
+      <c r="H3" s="23">
+        <f>E3/D3</f>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="I3" s="24">
+        <f>D3+D3*H3</f>
+        <v>130000</v>
+      </c>
+      <c r="J3" s="22" t="b">
+        <f>G3=I3</f>
+        <v>1</v>
+      </c>
+      <c r="K3" s="22" t="b">
+        <f>E3&gt;D3</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="22" t="b">
+        <f t="shared" ref="L3:L12" si="0">$S$3&lt;=C3</f>
+        <v>1</v>
+      </c>
+      <c r="M3" s="22" t="b">
+        <f t="shared" ref="M3:M12" si="1">$G3&gt;=$S$4</f>
+        <v>1</v>
+      </c>
+      <c r="N3" s="22">
+        <f>L3*M3</f>
+        <v>1</v>
+      </c>
+      <c r="O3" s="22" t="b">
+        <f>L3*M3=1</f>
+        <v>1</v>
+      </c>
+      <c r="P3" s="22" t="b">
+        <f>AND(L3,M3)</f>
+        <v>1</v>
+      </c>
+      <c r="R3" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="S3" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6">
+        <v>4</v>
+      </c>
+      <c r="D4" s="6">
+        <v>135000</v>
+      </c>
+      <c r="E4" s="7">
+        <v>12000</v>
+      </c>
+      <c r="F4" s="26">
+        <f t="shared" ref="F4:F12" si="2">C4</f>
+        <v>4</v>
+      </c>
+      <c r="G4" s="22">
+        <f t="shared" ref="G4:G12" si="3">D4+E4</f>
+        <v>147000</v>
+      </c>
+      <c r="H4" s="23">
+        <f t="shared" ref="H4:H12" si="4">E4/D4</f>
+        <v>8.8888888888888892E-2</v>
+      </c>
+      <c r="I4" s="24">
+        <f t="shared" ref="I4:I12" si="5">D4+D4*H4</f>
+        <v>147000</v>
+      </c>
+      <c r="J4" s="22" t="b">
+        <f t="shared" ref="J4:J12" si="6">G4=I4</f>
+        <v>1</v>
+      </c>
+      <c r="K4" s="22" t="b">
+        <f t="shared" ref="K4:K12" si="7">E4&gt;D4</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="22" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M4" s="22" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N4" s="22">
+        <f t="shared" ref="N4:N12" si="8">L4*M4</f>
+        <v>0</v>
+      </c>
+      <c r="O4" s="22" t="b">
+        <f t="shared" ref="O4:O12" si="9">L4*M4=1</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="22" t="b">
+        <f t="shared" ref="P4:P12" si="10">AND(L4,M4)</f>
+        <v>0</v>
+      </c>
+      <c r="R4" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="S4" s="13">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="6">
+        <v>2</v>
+      </c>
+      <c r="D5" s="6">
+        <v>75000</v>
+      </c>
+      <c r="E5" s="7">
+        <v>5000</v>
+      </c>
+      <c r="F5" s="26">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="G5" s="22">
+        <f t="shared" si="3"/>
+        <v>80000</v>
+      </c>
+      <c r="H5" s="23">
+        <f t="shared" si="4"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="I5" s="24">
+        <f t="shared" si="5"/>
+        <v>80000</v>
+      </c>
+      <c r="J5" s="22" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="K5" s="22" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="L5" s="22" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M5" s="22" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N5" s="22">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="O5" s="22" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="P5" s="22" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="6">
+        <v>6</v>
+      </c>
+      <c r="D6" s="6">
+        <v>110000</v>
+      </c>
+      <c r="E6" s="7">
+        <v>8000</v>
+      </c>
+      <c r="F6" s="26">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="G6" s="22">
+        <f t="shared" si="3"/>
+        <v>118000</v>
+      </c>
+      <c r="H6" s="23">
+        <f t="shared" si="4"/>
+        <v>7.2727272727272724E-2</v>
+      </c>
+      <c r="I6" s="24">
+        <f t="shared" si="5"/>
+        <v>118000</v>
+      </c>
+      <c r="J6" s="22" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="K6" s="22" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="L6" s="22" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M6" s="22" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N6" s="22">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="O6" s="22" t="b">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="P6" s="22" t="b">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="6">
+        <v>3</v>
+      </c>
+      <c r="D7" s="6">
+        <v>125000</v>
+      </c>
+      <c r="E7" s="7">
+        <v>11000</v>
+      </c>
+      <c r="F7" s="26">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="G7" s="22">
+        <f t="shared" si="3"/>
+        <v>136000</v>
+      </c>
+      <c r="H7" s="23">
+        <f t="shared" si="4"/>
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="I7" s="24">
+        <f t="shared" si="5"/>
+        <v>136000</v>
+      </c>
+      <c r="J7" s="22" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="K7" s="22" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="L7" s="22" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M7" s="22" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N7" s="22">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="O7" s="22" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="P7" s="22" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="6">
+        <v>7</v>
+      </c>
+      <c r="D8" s="6">
+        <v>90000</v>
+      </c>
+      <c r="E8" s="7">
+        <v>7000</v>
+      </c>
+      <c r="F8" s="26">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="G8" s="22">
+        <f t="shared" si="3"/>
+        <v>97000</v>
+      </c>
+      <c r="H8" s="23">
+        <f t="shared" si="4"/>
+        <v>7.7777777777777779E-2</v>
+      </c>
+      <c r="I8" s="24">
+        <f t="shared" si="5"/>
+        <v>97000</v>
+      </c>
+      <c r="J8" s="22" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="K8" s="22" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="L8" s="22" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M8" s="22" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N8" s="22">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="O8" s="22" t="b">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="P8" s="22" t="b">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="6">
+        <v>10</v>
+      </c>
+      <c r="D9" s="6">
+        <v>150000</v>
+      </c>
+      <c r="E9" s="7">
+        <v>15000</v>
+      </c>
+      <c r="F9" s="26">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="G9" s="22">
+        <f t="shared" si="3"/>
+        <v>165000</v>
+      </c>
+      <c r="H9" s="23">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="I9" s="24">
+        <f t="shared" si="5"/>
+        <v>165000</v>
+      </c>
+      <c r="J9" s="22" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="K9" s="22" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="L9" s="22" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M9" s="22" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N9" s="22">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="O9" s="22" t="b">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="P9" s="22" t="b">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="6">
+        <v>8</v>
+      </c>
+      <c r="D10" s="6">
+        <v>130000</v>
+      </c>
+      <c r="E10" s="7">
+        <v>13000</v>
+      </c>
+      <c r="F10" s="26">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="G10" s="22">
+        <f t="shared" si="3"/>
+        <v>143000</v>
+      </c>
+      <c r="H10" s="23">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="I10" s="24">
+        <f t="shared" si="5"/>
+        <v>143000</v>
+      </c>
+      <c r="J10" s="22" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="K10" s="22" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="22" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M10" s="22" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N10" s="22">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="O10" s="22" t="b">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="P10" s="22" t="b">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="6">
+        <v>3</v>
+      </c>
+      <c r="D11" s="6">
+        <v>140000</v>
+      </c>
+      <c r="E11" s="7">
+        <v>14000</v>
+      </c>
+      <c r="F11" s="26">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="G11" s="22">
+        <f t="shared" si="3"/>
+        <v>154000</v>
+      </c>
+      <c r="H11" s="23">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="I11" s="24">
+        <f t="shared" si="5"/>
+        <v>154000</v>
+      </c>
+      <c r="J11" s="22" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="K11" s="22" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="22" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M11" s="22" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N11" s="22">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="O11" s="22" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="P11" s="22" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="16">
+        <v>5</v>
+      </c>
+      <c r="D12" s="16">
+        <v>115000</v>
+      </c>
+      <c r="E12" s="17">
+        <v>9000</v>
+      </c>
+      <c r="F12" s="26">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="G12" s="22">
+        <f t="shared" si="3"/>
+        <v>124000</v>
+      </c>
+      <c r="H12" s="23">
+        <f t="shared" si="4"/>
+        <v>7.8260869565217397E-2</v>
+      </c>
+      <c r="I12" s="24">
+        <f t="shared" si="5"/>
+        <v>124000</v>
+      </c>
+      <c r="J12" s="22" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="K12" s="22" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="22" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M12" s="22" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N12" s="22">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="O12" s="22" t="b">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="P12" s="22" t="b">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="19">
+        <f>(C3+C4+C5+C6+C7+C8+C9+C10+C11+C12)/10</f>
+        <v>5.3</v>
+      </c>
+      <c r="D13" s="19">
+        <f t="shared" ref="D13:E13" si="11">(D3+D4+D5+D6+D7+D8+D9+D10+D11+D12)/10</f>
+        <v>119000</v>
+      </c>
+      <c r="E13" s="30">
+        <f t="shared" si="11"/>
+        <v>10400</v>
+      </c>
+    </row>
+    <row r="14" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="20">
+        <f>AVERAGE(C3:C12)</f>
+        <v>5.3</v>
+      </c>
+      <c r="D14" s="20">
+        <f>AVERAGE(D3:D12)</f>
+        <v>119000</v>
+      </c>
+      <c r="E14" s="32">
+        <f>AVERAGE(E3:E12)</f>
+        <v>10400</v>
+      </c>
+      <c r="F14" s="1">
+        <f t="shared" ref="D14:F14" si="12">AVERAGE(F3:F12)</f>
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="19">
+        <f>COUNT(C3:C12)</f>
+        <v>10</v>
+      </c>
+      <c r="D15" s="19">
+        <f>COUNT(D3:D12)</f>
+        <v>10</v>
+      </c>
+      <c r="E15" s="30">
+        <f>COUNT(E3:E12)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B16" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="18">
+        <f>COUNTIF(C3:C12,"&lt;=5")</f>
+        <v>6</v>
+      </c>
+      <c r="D16" s="18">
+        <f>COUNTIF(D3:D12,"&gt;=90000")</f>
+        <v>9</v>
+      </c>
+      <c r="E16" s="34"/>
+    </row>
+    <row r="17" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="35">
+        <f>COUNTIF(C3:C12,"&lt;="&amp;S3)</f>
+        <v>6</v>
+      </c>
+      <c r="D17" s="35">
+        <f>COUNTIF(D3:D12,"&gt;="&amp;S4)</f>
+        <v>9</v>
+      </c>
+      <c r="E17" s="36"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>